--- a/imports/list.xlsx
+++ b/imports/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmmmm\Downloads\kimeicho\kimeicho\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC75271D-40E9-4C75-96E6-DDBC8B5C55DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552934A7-9F72-4E24-AA20-EA5850610ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,17 +365,7 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-      </rPr>
-      <t>限定</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ゲンテイ</t>
-    </rPh>
+    <t>Vault</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -384,7 +374,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="181" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -535,17 +525,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>

--- a/imports/list.xlsx
+++ b/imports/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmmmm\Downloads\kimeicho\kimeicho\imports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552934A7-9F72-4E24-AA20-EA5850610ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0272A68F-52CE-4BE4-87B1-1B5D3B137C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,22 +173,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>了尊,尊了</t>
-    <rPh sb="0" eb="1">
-      <t>リョウ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ミコト</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>タケル</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>リョウ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>BLUE LOCK</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -215,35 +199,6 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>エリ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <r>
-      <t>Ai</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>遊,遊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="3"/>
-      </rPr>
-      <t>Ai</t>
-    </r>
-    <rPh sb="2" eb="3">
-      <t>アソ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>アソ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -297,19 +252,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>男二人きりでラブホテル、何も起きない</t>
-    <rPh sb="0" eb="3">
-      <t>オトコフタリ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ナニ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -366,6 +308,58 @@
   </si>
   <si>
     <t>Vault</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>了尊了</t>
+    <rPh sb="0" eb="1">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ミコト</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <r>
+      <t>Ai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>遊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>Ai</t>
+    </r>
+    <rPh sb="2" eb="3">
+      <t>アソ</t>
+    </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>男二人きりでラブホテル、何も起きないはずはある</t>
+    <rPh sb="0" eb="3">
+      <t>オトコフタリ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ナニ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -874,10 +868,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -903,10 +897,10 @@
         <v>8</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -926,13 +920,13 @@
         <v>36</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -949,16 +943,16 @@
         <v>7</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -975,16 +969,16 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -1004,13 +998,13 @@
         <v>36</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
@@ -2118,7 +2112,7 @@
     </row>
     <row r="20" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="13.8" x14ac:dyDescent="0.25">
